--- a/Claude outputs/Matriz_falas_O_Impostor.xlsx
+++ b/Claude outputs/Matriz_falas_O_Impostor.xlsx
@@ -1807,7 +1807,7 @@
     <t xml:space="preserve">Ouvi. Veio de dentro!</t>
   </si>
   <si>
-    <t xml:space="preserve">Ouvi.… Veio de dentro.</t>
+    <t xml:space="preserve">Ouvi… Veio de dentro.</t>
   </si>
   <si>
     <t xml:space="preserve">Ouvi. Veio de dentro…</t>
@@ -2035,7 +2035,7 @@
     <t xml:space="preserve">Entendido. Tem luz aí?!</t>
   </si>
   <si>
-    <t xml:space="preserve">Entendido.… Tem luz aí?</t>
+    <t xml:space="preserve">Entendido… Tem luz aí?</t>
   </si>
   <si>
     <t xml:space="preserve">Entendido. Tem luz aí…?</t>
@@ -9532,7 +9532,7 @@
     <t xml:space="preserve">Peso. Peso cai!</t>
   </si>
   <si>
-    <t xml:space="preserve">Peso.… Peso cai.</t>
+    <t xml:space="preserve">Peso… Peso cai.</t>
   </si>
   <si>
     <t xml:space="preserve">Peso. Peso cai…</t>
@@ -15076,7 +15076,7 @@
     <t xml:space="preserve">Tirei. Pesava!</t>
   </si>
   <si>
-    <t xml:space="preserve">Tirei.… Pesava.</t>
+    <t xml:space="preserve">Tirei… Pesava.</t>
   </si>
   <si>
     <t xml:space="preserve">Tirei. Pesava…</t>

--- a/Claude outputs/Matriz_falas_O_Impostor.xlsx
+++ b/Claude outputs/Matriz_falas_O_Impostor.xlsx
@@ -12034,28 +12034,28 @@
     <t xml:space="preserve">c5-p2-farol</t>
   </si>
   <si>
-    <t xml:space="preserve">Policial falou comigo</t>
+    <t xml:space="preserve">{pol} falou comigo</t>
   </si>
   <si>
     <t xml:space="preserve">o tempo todo</t>
   </si>
   <si>
-    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor. E o Policial falou comigo o tempo todo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor! E o Policial falou comigo o tempo todo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alguém parado na janela do corredor… no terceiro e no quarto. E o Policial falou comigo. O tempo todo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor. E o Policial falou comigo o tempo todo, não foi?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor. Frio danado aqui… E o Policial falou comigo o tempo todo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para o registro: no terceiro e no quarto, alguém parado na janela do corredor. O Policial falou comigo o tempo todo.</t>
+    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor. E {pol} falou comigo o tempo todo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor! E {pol} falou comigo o tempo todo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alguém parado na janela do corredor… no terceiro e no quarto. E {pol} falou comigo. O tempo todo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor. E {pol} falou comigo o tempo todo, não foi?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No terceiro e no quarto, alguém parado na janela do corredor. Frio danado aqui… E {pol} falou comigo o tempo todo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para o registro: no terceiro e no quarto, alguém parado na janela do corredor. {Pol} falou comigo o tempo todo.</t>
   </si>
   <si>
     <t xml:space="preserve">Enquadre fixo: O rádio chiou no vestíbulo. "Casa da Costa, aqui é o farol. … Contei seis clarões." E depois: "&lt;farol&gt;". Falante: o Faroleiro (masculino), pelo rádio; relata só vultos/posições, nunca rostos. ATENÇÃO: o mesmo D.farol entra também no Livro do Farol (paginasDoFarol, folha "A noite da leitura"), que é registro escrito: lá deve continuar a base, não a versão do tipo. "o Policial" é literal no código (não ficha {pol}); se o Policial for o jogador, talvez precise de ficha. Ingênuo "não foi?" pede confirmação ao grupo, não duvida do fato; se parecer suavizar o álibi, trocar por "desculpem".</t>
@@ -15397,7 +15397,7 @@
     <t xml:space="preserve">respondi</t>
   </si>
   <si>
-    <t xml:space="preserve">Policial</t>
+    <t xml:space="preserve">{a:pol}</t>
   </si>
   <si>
     <t xml:space="preserve">fim do corredor</t>
@@ -15406,25 +15406,25 @@
     <t xml:space="preserve">janela ocupada</t>
   </si>
   <si>
-    <t xml:space="preserve">E eu respondi ao Policial do fim do corredor, e o farol viu a janela ocupada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E eu respondi ao Policial do fim do corredor! E o farol viu a janela ocupada!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E eu respondi… ao Policial. Do fim do corredor. E o farol… viu a janela ocupada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E eu respondi ao Policial do fim do corredor! E o farol viu a janela ocupada, não viu?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondi ao Policial do fim do corredor. E o farol viu a janela ocupada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Essa umidade nos ossos… Eu respondi ao Policial do fim do corredor, e o farol viu a janela ocupada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Para a ata: respondi ao Policial do fim do corredor. O farol viu a janela ocupada.</t>
+    <t xml:space="preserve">E eu respondi {a:pol} do fim do corredor, e o farol viu a janela ocupada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E eu respondi {a:pol} do fim do corredor! E o farol viu a janela ocupada!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E eu respondi… {a:pol}. Do fim do corredor. E o farol… viu a janela ocupada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E eu respondi {a:pol} do fim do corredor! E o farol viu a janela ocupada, não viu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respondi {a:pol} do fim do corredor. E o farol viu a janela ocupada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Essa umidade nos ossos… Eu respondi {a:pol} do fim do corredor, e o farol viu a janela ocupada.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para a ata: respondi {a:pol} do fim do corredor. O farol viu a janela ocupada.</t>
   </si>
   <si>
     <t xml:space="preserve">Enquadre: &lt;i&gt;"…"&lt;/i&gt;, disse {jor}. Atenção: o original tem "ao Policial" em texto fixo, não ficha {a:pol}.</t>
